--- a/output/roomself_excel/6289.xlsx
+++ b/output/roomself_excel/6289.xlsx
@@ -476,10 +476,10 @@
         <v>1956</v>
       </c>
       <c r="E2" t="n">
-        <v>422</v>
+        <v>318</v>
       </c>
       <c r="F2" t="n">
-        <v>318</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3">

--- a/output/roomself_excel/6289.xlsx
+++ b/output/roomself_excel/6289.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,11 +525,49 @@
       <c r="D2" t="n">
         <v>1956</v>
       </c>
-      <c r="E2" t="n">
-        <v>318</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>234</v>
+        <v>332</v>
+      </c>
+      <c r="G2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>286</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>73</v>
+      </c>
+      <c r="M2" t="n">
+        <v>18</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>68</v>
+      </c>
+      <c r="P2" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +585,42 @@
       <c r="D3" t="n">
         <v>1480</v>
       </c>
-      <c r="E3" t="n">
-        <v>318</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>197</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>193</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>168</v>
+      </c>
+      <c r="M3" t="n">
+        <v>16</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +637,49 @@
       <c r="D4" t="n">
         <v>1848</v>
       </c>
-      <c r="E4" t="n">
-        <v>314</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>220</v>
+        <v>284</v>
+      </c>
+      <c r="G4" t="n">
+        <v>19</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>178</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>178</v>
+      </c>
+      <c r="M4" t="n">
+        <v>14</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>284</v>
+      </c>
+      <c r="P4" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/6289.xlsx
+++ b/output/roomself_excel/6289.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:AB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,66 @@
           <t>ExtWallWidth_4</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -569,6 +629,54 @@
       <c r="P2" t="n">
         <v>9</v>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>93</v>
+      </c>
+      <c r="T2" t="n">
+        <v>16</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>46</v>
+      </c>
+      <c r="X2" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -621,6 +729,30 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>118</v>
+      </c>
+      <c r="T3" t="n">
+        <v>16</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -681,6 +813,30 @@
       <c r="P4" t="n">
         <v>23</v>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>126</v>
+      </c>
+      <c r="T4" t="n">
+        <v>16</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
